--- a/backend/data/uploads/MES/2026-07-21_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-21_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EB16EC7-636E-40C3-BF10-44BF43BAC316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98D24739-11C3-4669-8348-87002E01246A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{B3318CBC-E279-40F5-A7C2-F82A0BE4569B}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{1A718DF0-77C0-4E95-8C68-37C16EEBCD5E}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD9F1BB8-40B2-4D1F-8536-49AE4CEB07B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A8F7AE0-B08E-413A-9C1F-4DB90A7ED615}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
